--- a/jira_export_2026-10-30.xlsx
+++ b/jira_export_2026-10-30.xlsx
@@ -723,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>75,900 €</t>
+          <t>77,349 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -737,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -770,7 +770,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>49,097 €</t>
+          <t>50,546 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>250.5</v>
+        <v>0</v>
       </c>
       <c r="O48" s="15" t="n">
         <v>876.75</v>
@@ -6237,13 +6237,13 @@
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>1786.1</v>
-      </c>
-      <c r="O77" s="16" t="n">
-        <v>909.9</v>
+        <v>0</v>
+      </c>
+      <c r="O77" s="12" t="n">
+        <v>2359</v>
       </c>
       <c r="P77" s="12" t="n">
-        <v>303.3</v>
+        <v>786.33</v>
       </c>
     </row>
     <row r="78">
@@ -13127,13 +13127,13 @@
       <c r="L180" s="17" t="inlineStr"/>
       <c r="M180" s="17" t="inlineStr"/>
       <c r="N180" s="18" t="n">
-        <v>64746.366</v>
+        <v>62709.766</v>
       </c>
       <c r="O180" s="18" t="n">
-        <v>75899.552</v>
+        <v>77348.65199999999</v>
       </c>
       <c r="P180" s="18" t="n">
-        <v>232.23</v>
+        <v>236.66</v>
       </c>
     </row>
   </sheetData>
@@ -15127,10 +15127,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>474057</v>
+        <v>472608</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>199231</v>
+        <v>197782</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>274826</v>
@@ -15177,10 +15177,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>226028</v>
+        <v>224579</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>132652</v>
+        <v>131203</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>93375</v>

--- a/jira_export_2026-10-30.xlsx
+++ b/jira_export_2026-10-30.xlsx
@@ -723,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>77,349 €</t>
+          <t>78,790 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -737,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -763,7 +763,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>26,592 €</t>
+          <t>28,033 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -936,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P180"/>
+  <dimension ref="A1:P181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -952,7 +952,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>963</v>
+        <v>0</v>
       </c>
       <c r="O29" s="12" t="n">
         <v>963</v>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="N35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="O35" s="16" t="n">
-        <v>675</v>
-      </c>
       <c r="P35" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>1068.45</v>
+        <v>628.5</v>
       </c>
       <c r="O40" s="15" t="n">
         <v>3582.45</v>
@@ -9979,22 +9979,22 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-25354</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Duncan HAMELIN</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>MAIRIE DE PLAN D'ORGON</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -10017,60 +10017,58 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>28/10/2025</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
         <v>12</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26768</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00141775</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
-        <v>606</v>
+        <v>0</v>
       </c>
       <c r="O130" s="15" t="n">
-        <v>606</v>
+        <v>400</v>
       </c>
       <c r="P130" s="15" t="n">
-        <v>2424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E131" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="n">
+        <v/>
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
@@ -10089,44 +10087,44 @@
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
         <v>12</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="O131" s="12" t="n">
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="P131" s="12" t="n">
-        <v>0</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
@@ -10136,11 +10134,13 @@
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
-        </is>
-      </c>
-      <c r="E132" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E132" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F132" s="14" t="inlineStr">
         <is>
@@ -10154,49 +10154,49 @@
       </c>
       <c r="H132" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
         <v>12</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>12</v>
+        <v>0.75</v>
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M132" s="14" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N132" s="15" t="n">
-        <v>3016.08</v>
-      </c>
-      <c r="O132" s="16" t="n">
-        <v>2471.51</v>
+        <v>0</v>
+      </c>
+      <c r="O132" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P132" s="15" t="n">
-        <v>205.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10229,54 +10229,54 @@
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0.75</v>
+        <v>12</v>
       </c>
       <c r="L133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M133" s="11" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N133" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" s="12" t="n">
-        <v>600</v>
+        <v>3016.08</v>
+      </c>
+      <c r="O133" s="16" t="n">
+        <v>2471.51</v>
       </c>
       <c r="P133" s="12" t="n">
-        <v>800</v>
+        <v>205.96</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10294,49 +10294,49 @@
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>13.5</v>
+        <v>0.75</v>
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M134" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N134" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O134" s="15" t="n">
-        <v>2497.125</v>
+        <v>600</v>
       </c>
       <c r="P134" s="15" t="n">
-        <v>184.97</v>
+        <v>800</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10369,44 +10369,44 @@
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>1</v>
+        <v>13.5</v>
       </c>
       <c r="L135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M135" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N135" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O135" s="12" t="n">
-        <v>0</v>
+        <v>2913.312</v>
       </c>
       <c r="P135" s="12" t="n">
-        <v>0</v>
+        <v>215.8</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10439,23 +10439,23 @@
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
         <v>15</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M136" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N136" s="15" t="n">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="L137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M137" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N137" s="12" t="n">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="L138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M138" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N138" s="15" t="n">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="L139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M139" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N139" s="12" t="n">
@@ -10681,22 +10681,22 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22120</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[CD 29 ] FLUX WFS</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
@@ -10709,27 +10709,35 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H140" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L140" s="14" t="inlineStr"/>
-      <c r="M140" s="14" t="inlineStr"/>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27365</t>
+        </is>
+      </c>
+      <c r="M140" s="14" t="inlineStr">
+        <is>
+          <t>491593</t>
+        </is>
+      </c>
       <c r="N140" s="15" t="n">
         <v>0</v>
       </c>
@@ -10743,22 +10751,22 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22120</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[CD 29 ] FLUX WFS</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10771,7 +10779,7 @@
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
@@ -10781,25 +10789,17 @@
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L141" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27373</t>
-        </is>
-      </c>
-      <c r="M141" s="11" t="inlineStr">
-        <is>
-          <t>466234</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L141" s="11" t="inlineStr"/>
+      <c r="M141" s="11" t="inlineStr"/>
       <c r="N141" s="12" t="n">
         <v>0</v>
       </c>
@@ -10813,12 +10813,12 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10846,28 +10846,28 @@
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="L142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M142" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N142" s="15" t="n">
@@ -10883,22 +10883,22 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -10916,28 +10916,28 @@
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
         <v>18</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="L143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M143" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N143" s="12" t="n">
@@ -10953,12 +10953,12 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
@@ -10981,23 +10981,35 @@
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H144" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H144" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L144" s="14" t="inlineStr"/>
-      <c r="M144" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L144" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M144" s="14" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N144" s="15" t="n">
         <v>0</v>
       </c>
@@ -11011,22 +11023,22 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -11039,35 +11051,23 @@
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H145" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr"/>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
         <v>19</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L145" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M145" s="11" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L145" s="11" t="inlineStr"/>
+      <c r="M145" s="11" t="inlineStr"/>
       <c r="N145" s="12" t="n">
         <v>0</v>
       </c>
@@ -11081,12 +11081,12 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E146" s="14" t="n">
@@ -11114,28 +11114,28 @@
       </c>
       <c r="H146" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
         <v>19</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M146" s="14" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N146" s="15" t="n">
@@ -11151,12 +11151,12 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -11184,28 +11184,28 @@
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
         <v>19</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M147" s="11" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N147" s="12" t="n">
@@ -11221,12 +11221,12 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
@@ -11236,13 +11236,11 @@
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E148" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E148" s="14" t="n">
+        <v/>
       </c>
       <c r="F148" s="14" t="inlineStr">
         <is>
@@ -11251,27 +11249,35 @@
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H148" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L148" s="14" t="inlineStr"/>
-      <c r="M148" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L148" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M148" s="14" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N148" s="15" t="n">
         <v>0</v>
       </c>
@@ -11285,26 +11291,28 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
-        </is>
-      </c>
-      <c r="E149" s="11" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F149" s="11" t="inlineStr">
         <is>
@@ -11323,14 +11331,14 @@
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L149" s="11" t="inlineStr"/>
       <c r="M149" s="11" t="inlineStr"/>
@@ -11347,22 +11355,22 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E150" s="14" t="n">
@@ -11380,7 +11388,7 @@
       </c>
       <c r="H150" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I150" s="14" t="inlineStr">
@@ -11409,22 +11417,22 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -11432,44 +11440,36 @@
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L151" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M151" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L151" s="11" t="inlineStr"/>
+      <c r="M151" s="11" t="inlineStr"/>
       <c r="N151" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O151" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P151" s="12" t="n">
@@ -11479,22 +11479,22 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E152" s="14" t="n">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="F152" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G152" s="14" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="H152" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
@@ -11528,18 +11528,18 @@
       </c>
       <c r="L152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M152" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N152" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O152" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O152" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P152" s="15" t="n">
@@ -11549,22 +11549,22 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
@@ -11587,17 +11587,25 @@
       </c>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K153" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="L153" s="11" t="inlineStr"/>
-      <c r="M153" s="11" t="inlineStr"/>
+      <c r="L153" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M153" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N153" s="12" t="n">
         <v>0</v>
       </c>
@@ -11611,12 +11619,12 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr">
@@ -11626,7 +11634,7 @@
       </c>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E154" s="14" t="n">
@@ -11649,14 +11657,14 @@
       </c>
       <c r="I154" s="14" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J154" s="14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K154" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L154" s="14" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -11673,22 +11681,22 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -11711,14 +11719,14 @@
       </c>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J155" s="11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L155" s="11" t="inlineStr"/>
       <c r="M155" s="11" t="inlineStr"/>
@@ -11735,12 +11743,12 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C156" s="14" t="inlineStr">
@@ -11750,7 +11758,7 @@
       </c>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E156" s="14" t="n">
@@ -11773,14 +11781,14 @@
       </c>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J156" s="14" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K156" s="14" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L156" s="14" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -11797,12 +11805,12 @@
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr">
@@ -11812,7 +11820,7 @@
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E157" s="11" t="n">
@@ -11830,19 +11838,19 @@
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J157" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K157" s="11" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="L157" s="11" t="inlineStr"/>
       <c r="M157" s="11" t="inlineStr"/>
@@ -11859,12 +11867,12 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr">
@@ -11874,7 +11882,7 @@
       </c>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E158" s="14" t="n">
@@ -11887,35 +11895,27 @@
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H158" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J158" s="14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K158" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L158" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M158" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L158" s="14" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
       <c r="N158" s="15" t="n">
         <v>0</v>
       </c>
@@ -11929,22 +11929,22 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E159" s="11" t="n">
@@ -11957,23 +11957,35 @@
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H159" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H159" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I159" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J159" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L159" s="11" t="inlineStr"/>
-      <c r="M159" s="11" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L159" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M159" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N159" s="12" t="n">
         <v>0</v>
       </c>
@@ -11987,12 +11999,12 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr">
@@ -12002,7 +12014,7 @@
       </c>
       <c r="D160" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E160" s="14" t="n">
@@ -12018,61 +12030,49 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H160" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H160" s="14" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J160" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K160" s="14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L160" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M160" s="14" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>3.75</v>
+      </c>
+      <c r="L160" s="14" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
       <c r="N160" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O160" s="15" t="n">
-        <v>2750</v>
+        <v>0</v>
       </c>
       <c r="P160" s="15" t="n">
-        <v>261.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E161" s="11" t="n">
@@ -12085,62 +12085,68 @@
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H161" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H161" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J161" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K161" s="11" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="L161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M161" s="11" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N161" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O161" s="12" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="P161" s="12" t="n">
-        <v>0</v>
+        <v>261.9</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C162" s="14" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C162" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E162" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E162" s="14" t="n">
+        <v/>
       </c>
       <c r="F162" s="14" t="inlineStr">
         <is>
@@ -12149,27 +12155,31 @@
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H162" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J162" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K162" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L162" s="14" t="inlineStr"/>
-      <c r="M162" s="14" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L162" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M162" s="14" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N162" s="15" t="n">
         <v>0</v>
       </c>
@@ -12183,21 +12193,25 @@
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="E163" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F163" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -12205,20 +12219,24 @@
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H163" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H163" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I163" s="11" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J163" s="11" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K163" s="11" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="L163" s="11" t="inlineStr"/>
       <c r="M163" s="11" t="inlineStr"/>
@@ -12235,46 +12253,50 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>PSC-1357</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C164" s="14" t="inlineStr"/>
-      <c r="D164" s="14" t="inlineStr"/>
+      <c r="D164" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
       <c r="E164" s="14" t="inlineStr"/>
-      <c r="F164" s="14" t="inlineStr"/>
+      <c r="F164" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G164" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr"/>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J164" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K164" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-36143</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L164" s="14" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
       <c r="N164" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O164" s="15" t="n">
-        <v>210.8</v>
+        <v>0</v>
       </c>
       <c r="P164" s="15" t="n">
         <v>0</v>
@@ -12283,50 +12305,46 @@
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1357</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr"/>
-      <c r="D165" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE VALENCAY</t>
-        </is>
-      </c>
+      <c r="D165" s="11" t="inlineStr"/>
       <c r="E165" s="11" t="inlineStr"/>
-      <c r="F165" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+      <c r="F165" s="11" t="inlineStr"/>
       <c r="G165" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr"/>
       <c r="I165" s="11" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="J165" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L165" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L165" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36143</t>
+        </is>
+      </c>
       <c r="M165" s="11" t="inlineStr"/>
       <c r="N165" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O165" s="12" t="n">
-        <v>0</v>
+        <v>210.8</v>
       </c>
       <c r="P165" s="12" t="n">
         <v>0</v>
@@ -12335,18 +12353,18 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C166" s="14" t="inlineStr"/>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr"/>
@@ -12363,7 +12381,7 @@
       <c r="H166" s="14" t="inlineStr"/>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J166" s="14" t="n">
@@ -12387,18 +12405,18 @@
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr"/>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr"/>
@@ -12409,56 +12427,48 @@
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr"/>
       <c r="I167" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J167" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K167" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L167" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M167" s="11" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+      <c r="L167" s="11" t="inlineStr"/>
+      <c r="M167" s="11" t="inlineStr"/>
       <c r="N167" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O167" s="16" t="n">
-        <v>350</v>
+        <v>0</v>
+      </c>
+      <c r="O167" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P167" s="12" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C168" s="14" t="inlineStr"/>
       <c r="D168" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr"/>
@@ -12469,13 +12479,13 @@
       </c>
       <c r="G168" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr"/>
       <c r="I168" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J168" s="14" t="n">
@@ -12484,33 +12494,41 @@
       <c r="K168" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L168" s="14" t="inlineStr"/>
-      <c r="M168" s="14" t="inlineStr"/>
+      <c r="L168" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M168" s="14" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N168" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O168" s="15" t="n">
-        <v>0</v>
+        <v>450</v>
+      </c>
+      <c r="O168" s="16" t="n">
+        <v>350</v>
       </c>
       <c r="P168" s="15" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="10" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C169" s="11" t="inlineStr"/>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr"/>
@@ -12521,31 +12539,23 @@
       </c>
       <c r="G169" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr"/>
       <c r="I169" s="11" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J169" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K169" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L169" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M169" s="11" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L169" s="11" t="inlineStr"/>
+      <c r="M169" s="11" t="inlineStr"/>
       <c r="N169" s="12" t="n">
         <v>0</v>
       </c>
@@ -12559,18 +12569,18 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B170" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C170" s="14" t="inlineStr"/>
       <c r="D170" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr"/>
@@ -12581,48 +12591,56 @@
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr"/>
       <c r="I170" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J170" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K170" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L170" s="14" t="inlineStr"/>
-      <c r="M170" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L170" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M170" s="14" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N170" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O170" s="15" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P170" s="15" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="10" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C171" s="11" t="inlineStr"/>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr"/>
@@ -12639,14 +12657,14 @@
       <c r="H171" s="11" t="inlineStr"/>
       <c r="I171" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J171" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K171" s="11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L171" s="11" t="inlineStr"/>
       <c r="M171" s="11" t="inlineStr"/>
@@ -12663,18 +12681,18 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B172" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C172" s="14" t="inlineStr"/>
       <c r="D172" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E172" s="14" t="inlineStr"/>
@@ -12691,14 +12709,14 @@
       <c r="H172" s="14" t="inlineStr"/>
       <c r="I172" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J172" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K172" s="14" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="L172" s="14" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -12715,18 +12733,18 @@
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C173" s="11" t="inlineStr"/>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr"/>
@@ -12737,31 +12755,23 @@
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr"/>
       <c r="I173" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J173" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K173" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L173" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34335</t>
-        </is>
-      </c>
-      <c r="M173" s="11" t="inlineStr">
-        <is>
-          <t>00168072</t>
-        </is>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="L173" s="11" t="inlineStr"/>
+      <c r="M173" s="11" t="inlineStr"/>
       <c r="N173" s="12" t="n">
         <v>0</v>
       </c>
@@ -12775,18 +12785,18 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B174" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C174" s="14" t="inlineStr"/>
       <c r="D174" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E174" s="14" t="inlineStr"/>
@@ -12803,23 +12813,23 @@
       <c r="H174" s="14" t="inlineStr"/>
       <c r="I174" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J174" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K174" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L174" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34335</t>
         </is>
       </c>
       <c r="M174" s="14" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00168072</t>
         </is>
       </c>
       <c r="N174" s="15" t="n">
@@ -12835,18 +12845,18 @@
     <row r="175">
       <c r="A175" s="10" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C175" s="11" t="inlineStr"/>
       <c r="D175" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr"/>
@@ -12857,23 +12867,31 @@
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H175" s="11" t="inlineStr"/>
       <c r="I175" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J175" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K175" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L175" s="11" t="inlineStr"/>
-      <c r="M175" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L175" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M175" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N175" s="12" t="n">
         <v>0</v>
       </c>
@@ -12887,18 +12905,18 @@
     <row r="176">
       <c r="A176" s="13" t="inlineStr">
         <is>
-          <t>PSC-1119</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B176" s="14" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C176" s="14" t="inlineStr"/>
       <c r="D176" s="14" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E176" s="14" t="inlineStr"/>
@@ -12909,31 +12927,23 @@
       </c>
       <c r="G176" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H176" s="14" t="inlineStr"/>
       <c r="I176" s="14" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J176" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K176" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L176" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-30236</t>
-        </is>
-      </c>
-      <c r="M176" s="14" t="inlineStr">
-        <is>
-          <t>00152992</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L176" s="14" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
       <c r="N176" s="15" t="n">
         <v>0</v>
       </c>
@@ -12947,18 +12957,18 @@
     <row r="177">
       <c r="A177" s="10" t="inlineStr">
         <is>
-          <t>PSC-1060</t>
+          <t>PSC-1119</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="C177" s="11" t="inlineStr"/>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr"/>
@@ -12969,23 +12979,31 @@
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H177" s="11" t="inlineStr"/>
       <c r="I177" s="11" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="J177" s="11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K177" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L177" s="11" t="inlineStr"/>
-      <c r="M177" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L177" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-30236</t>
+        </is>
+      </c>
+      <c r="M177" s="11" t="inlineStr">
+        <is>
+          <t>00152992</t>
+        </is>
+      </c>
       <c r="N177" s="12" t="n">
         <v>0</v>
       </c>
@@ -12999,18 +13017,18 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1060</t>
         </is>
       </c>
       <c r="B178" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="C178" s="14" t="inlineStr"/>
       <c r="D178" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="E178" s="14" t="inlineStr"/>
@@ -13021,31 +13039,23 @@
       </c>
       <c r="G178" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H178" s="14" t="inlineStr"/>
       <c r="I178" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="J178" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K178" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L178" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-26768</t>
-        </is>
-      </c>
-      <c r="M178" s="14" t="inlineStr">
-        <is>
-          <t>00141775</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L178" s="14" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
       <c r="N178" s="15" t="n">
         <v>0</v>
       </c>
@@ -13059,18 +13069,18 @@
     <row r="179">
       <c r="A179" s="10" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1047</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="C179" s="11" t="inlineStr"/>
       <c r="D179" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr"/>
@@ -13081,59 +13091,119 @@
       </c>
       <c r="G179" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H179" s="11" t="inlineStr"/>
       <c r="I179" s="11" t="inlineStr">
         <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="J179" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K179" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L179" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-26768</t>
+        </is>
+      </c>
+      <c r="M179" s="11" t="inlineStr">
+        <is>
+          <t>00141775</t>
+        </is>
+      </c>
+      <c r="N179" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="P179" s="12" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="13" t="inlineStr">
+        <is>
+          <t>PSC-850</t>
+        </is>
+      </c>
+      <c r="B180" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="C180" s="14" t="inlineStr"/>
+      <c r="D180" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="E180" s="14" t="inlineStr"/>
+      <c r="F180" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G180" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H180" s="14" t="inlineStr"/>
+      <c r="I180" s="14" t="inlineStr">
+        <is>
           <t>10/06/2025</t>
         </is>
       </c>
-      <c r="J179" s="11" t="n">
+      <c r="J180" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="K179" s="11" t="n">
+      <c r="K180" s="14" t="n">
         <v>0.75</v>
       </c>
-      <c r="L179" s="11" t="inlineStr"/>
-      <c r="M179" s="11" t="inlineStr"/>
-      <c r="N179" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O179" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P179" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="17" t="inlineStr">
+      <c r="L180" s="14" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+      <c r="N180" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B180" s="17" t="inlineStr"/>
-      <c r="C180" s="17" t="inlineStr"/>
-      <c r="D180" s="17" t="inlineStr"/>
-      <c r="E180" s="17" t="inlineStr"/>
-      <c r="F180" s="17" t="inlineStr"/>
-      <c r="G180" s="17" t="inlineStr"/>
-      <c r="H180" s="17" t="inlineStr"/>
-      <c r="I180" s="17" t="inlineStr"/>
-      <c r="J180" s="17" t="inlineStr"/>
-      <c r="K180" s="17" t="inlineStr"/>
-      <c r="L180" s="17" t="inlineStr"/>
-      <c r="M180" s="17" t="inlineStr"/>
-      <c r="N180" s="18" t="n">
-        <v>62709.766</v>
-      </c>
-      <c r="O180" s="18" t="n">
-        <v>77348.65199999999</v>
-      </c>
-      <c r="P180" s="18" t="n">
-        <v>236.66</v>
+      <c r="B181" s="17" t="inlineStr"/>
+      <c r="C181" s="17" t="inlineStr"/>
+      <c r="D181" s="17" t="inlineStr"/>
+      <c r="E181" s="17" t="inlineStr"/>
+      <c r="F181" s="17" t="inlineStr"/>
+      <c r="G181" s="17" t="inlineStr"/>
+      <c r="H181" s="17" t="inlineStr"/>
+      <c r="I181" s="17" t="inlineStr"/>
+      <c r="J181" s="17" t="inlineStr"/>
+      <c r="K181" s="17" t="inlineStr"/>
+      <c r="L181" s="17" t="inlineStr"/>
+      <c r="M181" s="17" t="inlineStr"/>
+      <c r="N181" s="18" t="n">
+        <v>60556.81600000001</v>
+      </c>
+      <c r="O181" s="18" t="n">
+        <v>78789.83899999999</v>
+      </c>
+      <c r="P181" s="18" t="n">
+        <v>241.07</v>
       </c>
     </row>
   </sheetData>
@@ -13314,6 +13384,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId176"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15127,16 +15198,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>472608</v>
+        <v>471566</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>197782</v>
+        <v>196816</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>274826</v>
+        <v>274751</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>216337</v>
+        <v>216262</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>16308</v>
@@ -15152,16 +15223,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>244929</v>
+        <v>243888</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>63479</v>
+        <v>62513</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>181450</v>
+        <v>181375</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>162238</v>
+        <v>162163</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>

--- a/jira_export_2026-10-30.xlsx
+++ b/jira_export_2026-10-30.xlsx
@@ -15608,10 +15608,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>470515</v>
+        <v>470711</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>196078</v>
+        <v>196274</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>274436</v>
@@ -15658,10 +15658,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>223912</v>
+        <v>224108</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>130851</v>
+        <v>131047</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>93061</v>
@@ -15687,7 +15687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15711,7 +15711,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 30 commande(s)</t>
+          <t>Épics créées ce mois — 31 commande(s)</t>
         </is>
       </c>
     </row>
@@ -16212,22 +16212,22 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36835</t>
+          <t>PDMDEP-36581</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36831</t>
+          <t>PDMDEP-36572</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>RENNES METROPOLE</t>
+          <t>MAIRIE EYMET</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -16247,32 +16247,32 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00186424</t>
+          <t>00185751</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>0</v>
+        <v>1667.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36659</t>
+          <t>PDMDEP-36474</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36653</t>
+          <t>PDMDEP-36465</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>27/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Commune de Dreux</t>
+          <t>COMMUNE DE SALON DE PROVENCE</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -16292,32 +16292,32 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00186097</t>
+          <t>00185032</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>8805</v>
+        <v>4685</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36771</t>
+          <t>PDMDEP-36746</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36767</t>
+          <t>PDMDEP-36309</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE D OYONNAX</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -16330,39 +16330,35 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>00186190</t>
+          <t>00184194</t>
         </is>
       </c>
       <c r="I17" s="25" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36757</t>
+          <t>PDMDEP-36645</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36748</t>
+          <t>PDMDEP-36639</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CHATILLON SUR CHALARONNE</t>
+          <t>Ville de Fleury  Les Aubrais</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -16372,7 +16368,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -16382,32 +16378,32 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>00185435</t>
+          <t>00186007</t>
         </is>
       </c>
       <c r="I18" s="26" t="n">
-        <v>735</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36746</t>
+          <t>PDMDEP-36835</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36309</t>
+          <t>PDMDEP-36831</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D OYONNAX</t>
+          <t>RENNES METROPOLE</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -16420,8 +16416,16 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr"/>
-      <c r="H19" s="14" t="inlineStr"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>00186424</t>
+        </is>
+      </c>
       <c r="I19" s="25" t="n">
         <v>0</v>
       </c>
@@ -16429,22 +16433,22 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36581</t>
+          <t>PDMDEP-36659</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36572</t>
+          <t>PDMDEP-36653</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE EYMET</t>
+          <t>Commune de Dreux</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -16454,7 +16458,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -16464,32 +16468,32 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>00185751</t>
+          <t>00186097</t>
         </is>
       </c>
       <c r="I20" s="26" t="n">
-        <v>1667.5</v>
+        <v>8805</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36474</t>
+          <t>PDMDEP-36771</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36465</t>
+          <t>PDMDEP-36767</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SALON DE PROVENCE</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -16499,7 +16503,7 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -16509,32 +16513,32 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>00185032</t>
+          <t>00186190</t>
         </is>
       </c>
       <c r="I21" s="25" t="n">
-        <v>4685</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36645</t>
+          <t>PDMDEP-36614</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36639</t>
+          <t>PDMDEP-36608</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>27/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Ville de Fleury  Les Aubrais</t>
+          <t>COMMUNE DE MARSEILLAN</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -16554,32 +16558,32 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>00186007</t>
+          <t>00185893</t>
         </is>
       </c>
       <c r="I22" s="26" t="n">
-        <v>3250</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36614</t>
+          <t>PDMDEP-36757</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36608</t>
+          <t>PDMDEP-36748</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MARSEILLAN</t>
+          <t>MAIRIE DE CHATILLON SUR CHALARONNE</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -16589,7 +16593,7 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
@@ -16599,32 +16603,32 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>00185893</t>
+          <t>00185435</t>
         </is>
       </c>
       <c r="I23" s="25" t="n">
-        <v>6800</v>
+        <v>735</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36428</t>
+          <t>PDMDEP-36197</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36421</t>
+          <t>PDMDEP-36190</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -16634,7 +16638,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -16644,32 +16648,32 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>00184334</t>
+          <t>00183894</t>
         </is>
       </c>
       <c r="I24" s="26" t="n">
-        <v>0</v>
+        <v>5718</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36427</t>
+          <t>PDMDEP-36797</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36421</t>
+          <t>PDMDEP-36793</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -16689,32 +16693,32 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>00184846</t>
+          <t>00186294</t>
         </is>
       </c>
       <c r="I25" s="25" t="n">
-        <v>3575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36402</t>
+          <t>PDMDEP-36781</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36398</t>
+          <t>PDMDEP-36776</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTÉ DE COMMUNES DE VIE ET BOULOGNE</t>
+          <t xml:space="preserve">Ville de Chartres </t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -16734,7 +16738,7 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>00184748</t>
+          <t>00186194</t>
         </is>
       </c>
       <c r="I26" s="26" t="n">
@@ -16744,22 +16748,22 @@
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36148</t>
+          <t>PDMDEP-36780</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36144</t>
+          <t>PDMDEP-36776</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
+          <t xml:space="preserve">Ville de Chartres </t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -16779,32 +16783,32 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>00183228</t>
+          <t>00186195</t>
         </is>
       </c>
       <c r="I27" s="25" t="n">
-        <v>2310</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36497</t>
+          <t>PDMDEP-36555</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36493</t>
+          <t>PDMDEP-36549</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE SEINE ET MARNE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -16824,32 +16828,32 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>00185186</t>
+          <t>00185556</t>
         </is>
       </c>
       <c r="I28" s="26" t="n">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36780</t>
+          <t>PDMDEP-36427</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36776</t>
+          <t>PDMDEP-36421</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ville de Chartres </t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -16869,32 +16873,32 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>00186195</t>
+          <t>00184846</t>
         </is>
       </c>
       <c r="I29" s="25" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36781</t>
+          <t>PDMDEP-36428</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36776</t>
+          <t>PDMDEP-36421</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ville de Chartres </t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -16914,32 +16918,32 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>00186194</t>
+          <t>00184334</t>
         </is>
       </c>
       <c r="I30" s="26" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36197</t>
+          <t>PDMDEP-36439</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36190</t>
+          <t>PDMDEP-36435</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+          <t>COMMUNE D'ANGERS</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
@@ -16949,7 +16953,7 @@
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
@@ -16959,32 +16963,32 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>00183894</t>
+          <t>00184863</t>
         </is>
       </c>
       <c r="I31" s="25" t="n">
-        <v>5718</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36797</t>
+          <t>PDMDEP-36148</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36793</t>
+          <t>PDMDEP-36144</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -17004,32 +17008,32 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>00186294</t>
+          <t>00183228</t>
         </is>
       </c>
       <c r="I32" s="26" t="n">
-        <v>0</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36439</t>
+          <t>PDMDEP-36497</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-36435</t>
+          <t>PDMDEP-36493</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANGERS</t>
+          <t>DEPARTEMENT DE SEINE ET MARNE</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
@@ -17049,32 +17053,32 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>00184863</t>
+          <t>00185186</t>
         </is>
       </c>
       <c r="I33" s="25" t="n">
-        <v>4000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36555</t>
+          <t>PDMDEP-36402</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-36549</t>
+          <t>PDMDEP-36398</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNAUTÉ DE COMMUNES DE VIE ET BOULOGNE</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -17094,38 +17098,58 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>00185556</t>
+          <t>00184748</t>
         </is>
       </c>
       <c r="I34" s="26" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="17" t="n"/>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="17" t="n"/>
-      <c r="G35" s="17" t="n"/>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>30 commande(s)</t>
-        </is>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>54126</v>
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36840</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36421</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr"/>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>00184335</t>
+        </is>
+      </c>
+      <c r="I35" s="25" t="n">
+        <v>2250</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B36" s="17" t="n"/>
@@ -17136,17 +17160,17 @@
       <c r="G36" s="17" t="n"/>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>11 commande(s)</t>
+          <t>31 commande(s)</t>
         </is>
       </c>
       <c r="I36" s="24" t="n">
-        <v>16853</v>
+        <v>54322</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B37" s="17" t="n"/>
@@ -17157,11 +17181,32 @@
       <c r="G37" s="17" t="n"/>
       <c r="H37" s="17" t="inlineStr">
         <is>
+          <t>12 commande(s)</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>16853</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
+      <c r="G38" s="17" t="n"/>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
           <t>18 commande(s)</t>
         </is>
       </c>
-      <c r="I37" s="24" t="n">
-        <v>34172</v>
+      <c r="I38" s="24" t="n">
+        <v>34368</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-10-30.xlsx
+++ b/jira_export_2026-10-30.xlsx
@@ -723,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>79,608 €</t>
+          <t>79,712 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -737,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -763,7 +763,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>28,418 €</t>
+          <t>28,522 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>1456</v>
+        <v>1560</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
@@ -13604,10 +13604,10 @@
         <v>56916.716</v>
       </c>
       <c r="O187" s="18" t="n">
-        <v>79608.06899999999</v>
+        <v>79712.06899999999</v>
       </c>
       <c r="P187" s="18" t="n">
-        <v>233.57</v>
+        <v>233.88</v>
       </c>
     </row>
   </sheetData>
@@ -15608,16 +15608,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>470711</v>
+        <v>470607</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>196274</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>274436</v>
+        <v>274332</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>216262</v>
+        <v>216158</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>15994</v>
@@ -15633,16 +15633,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>243502</v>
+        <v>243398</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>62127</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>181375</v>
+        <v>181271</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>162163</v>
+        <v>162059</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>
